--- a/PlayGround/Verification Freq_Metrics/FreqMetrics_Reference_Python.xlsx
+++ b/PlayGround/Verification Freq_Metrics/FreqMetrics_Reference_Python.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>ms_db</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>ms_matlab</t>
+          <t>ms_db_matlab</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>d_ms</t>
+          <t>d_ms_db</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1.046099869505576</v>
+        <v>0.3914629584023722</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -612,7 +612,7 @@
         <v>-102.6392928</v>
       </c>
       <c r="U2" t="n">
-        <v>1.04609987</v>
+        <v>0.391462962507633</v>
       </c>
       <c r="V2" t="n">
         <v>5.366491609</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>-4.944240572513081e-10</v>
+        <v>-4.105260853481951e-09</v>
       </c>
       <c r="Z2" t="n">
         <v>-4.747789343007014e-06</v>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1.046504191560446</v>
+        <v>0.394819443134366</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -696,7 +696,7 @@
         <v>-103.9071491</v>
       </c>
       <c r="U3" t="n">
-        <v>1.046504192</v>
+        <v>0.3948194467826255</v>
       </c>
       <c r="V3" t="n">
         <v>5.459959347</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>-4.395541708390738e-10</v>
+        <v>-3.648259583322044e-09</v>
       </c>
       <c r="Z3" t="n">
         <v>-6.813857376108956e-06</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1.046382513378818</v>
+        <v>0.3938094665735919</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -780,7 +780,7 @@
         <v>-104.6564626</v>
       </c>
       <c r="U4" t="n">
-        <v>1.046382513</v>
+        <v>0.3938094634290724</v>
       </c>
       <c r="V4" t="n">
         <v>5.441612907</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>3.788178659647201e-10</v>
+        <v>3.144519533648804e-09</v>
       </c>
       <c r="Z4" t="n">
         <v>-3.237302041547707e-06</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1.046297944544844</v>
+        <v>0.3931074429499301</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -864,7 +864,7 @@
         <v>-105.3398161</v>
       </c>
       <c r="U5" t="n">
-        <v>1.046297945</v>
+        <v>0.3931074467284312</v>
       </c>
       <c r="V5" t="n">
         <v>5.435582486</v>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>-4.55156357048736e-10</v>
+        <v>-3.778501067586149e-09</v>
       </c>
       <c r="Z5" t="n">
         <v>-5.580405569638458e-06</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1.494325369665555</v>
+        <v>3.488903393569196</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>1.49432537</v>
+        <v>3.488903395513185</v>
       </c>
       <c r="V6" t="n">
         <v>5.40264822</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>-3.344451382503166e-10</v>
+        <v>-1.943989857977613e-09</v>
       </c>
       <c r="Z6" t="n">
         <v>-4.912398585688038e-07</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.493888290528602</v>
+        <v>3.486362463364422</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>1.493888291</v>
+        <v>3.486362466105266</v>
       </c>
       <c r="V7" t="n">
         <v>5.3407357</v>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>-4.713984758097922e-10</v>
+        <v>-2.740843996207332e-09</v>
       </c>
       <c r="Z7" t="n">
         <v>0.0001154716894138375</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1.492228224500121</v>
+        <v>3.476705002426006</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>1.492228225</v>
+        <v>3.476705005335678</v>
       </c>
       <c r="V8" t="n">
         <v>5.408858482</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
-        <v>-4.998790270605014e-10</v>
+        <v>-2.909671614759191e-09</v>
       </c>
       <c r="Z8" t="n">
         <v>0.0001437479983357193</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.491706841213585</v>
+        <v>3.473669629582873</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>1.491706841</v>
+        <v>3.473669628339213</v>
       </c>
       <c r="V9" t="n">
         <v>5.333242353</v>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>2.135851495665975e-10</v>
+        <v>1.243660285865644e-09</v>
       </c>
       <c r="Z9" t="n">
         <v>7.101076682047847e-05</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.218484624679864</v>
+        <v>1.716401069121117</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>1.218484625</v>
+        <v>1.716401071403185</v>
       </c>
       <c r="V10" t="n">
         <v>5.312241734</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="n">
-        <v>-3.201359177751328e-10</v>
+        <v>-2.282068534142923e-09</v>
       </c>
       <c r="Z10" t="n">
         <v>1.06207590278018e-07</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.217956111933522</v>
+        <v>1.712632782546316</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>1.217956112</v>
+        <v>1.712632783020404</v>
       </c>
       <c r="V11" t="n">
         <v>5.292423122</v>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="n">
-        <v>-6.64777122239002e-11</v>
+        <v>-4.740876580200393e-10</v>
       </c>
       <c r="Z11" t="n">
         <v>1.400835859755034e-06</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.218307427475926</v>
+        <v>1.715137838342824</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>1.218307427</v>
+        <v>1.715137834949721</v>
       </c>
       <c r="V12" t="n">
         <v>5.352348404</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>4.759261873488185e-10</v>
+        <v>3.393102909754475e-09</v>
       </c>
       <c r="Z12" t="n">
         <v>1.730052606951915e-06</v>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.218361512858704</v>
+        <v>1.715523430048071</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>1.218361513</v>
+        <v>1.715523431055396</v>
       </c>
       <c r="V13" t="n">
         <v>5.391603579</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>-1.412965300318092e-10</v>
+        <v>-1.007324890167638e-09</v>
       </c>
       <c r="Z13" t="n">
         <v>1.520724920212047e-06</v>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.135547336622469</v>
+        <v>1.104104860158346</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="U14" t="n">
-        <v>1.135547337</v>
+        <v>1.104104863046109</v>
       </c>
       <c r="V14" t="n">
         <v>5.002295568</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>-3.775308954345746e-10</v>
+        <v>-2.887763139725052e-09</v>
       </c>
       <c r="Z14" t="n">
         <v>-4.850441239767633e-07</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.13595623378808</v>
+        <v>1.107231983301305</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>1.135956234</v>
+        <v>1.107231984921718</v>
       </c>
       <c r="V15" t="n">
         <v>5.104032157</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>-2.119204811634745e-10</v>
+        <v>-1.620412692915352e-09</v>
       </c>
       <c r="Z15" t="n">
         <v>2.597702404294466e-06</v>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.136285492880268</v>
+        <v>1.109749240266998</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>1.136285493</v>
+        <v>1.10974924118224</v>
       </c>
       <c r="V16" t="n">
         <v>5.164575542</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>-1.197317800460951e-10</v>
+        <v>-9.152427704606225e-10</v>
       </c>
       <c r="Z16" t="n">
         <v>4.296297264616555e-07</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.135347694777939</v>
+        <v>1.102577649953364</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>1.135347695</v>
+        <v>1.102577651652228</v>
       </c>
       <c r="V17" t="n">
         <v>5.078635453</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>-2.220614803150056e-10</v>
+        <v>-1.698864160459834e-09</v>
       </c>
       <c r="Z17" t="n">
         <v>2.390941725494145e-06</v>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1.096151757708622</v>
+        <v>0.7974136919618326</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>1.096151758</v>
+        <v>0.7974136942707077</v>
       </c>
       <c r="V18" t="n">
         <v>4.840331377</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>-2.913780328128723e-10</v>
+        <v>-2.308875091117102e-09</v>
       </c>
       <c r="Z18" t="n">
         <v>1.221467146983457e-06</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1.097020030201262</v>
+        <v>0.8042911463249025</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>1.09702003</v>
+        <v>0.8042911447313633</v>
       </c>
       <c r="V19" t="n">
         <v>4.964727979</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>2.012625621716779e-10</v>
+        <v>1.593539189492788e-09</v>
       </c>
       <c r="Z19" t="n">
         <v>2.688750499579839e-06</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1.096426386369529</v>
+        <v>0.7995895726792472</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>1.096426386</v>
+        <v>0.7995895697518397</v>
       </c>
       <c r="V20" t="n">
         <v>4.890091355</v>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="n">
-        <v>3.695288519622864e-10</v>
+        <v>2.92740753859988e-09</v>
       </c>
       <c r="Z20" t="n">
         <v>4.575518923743971e-07</v>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1.096439475033096</v>
+        <v>0.7996932604508149</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>1.096439475</v>
+        <v>0.7996932601886282</v>
       </c>
       <c r="V21" t="n">
         <v>4.909537038</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="n">
-        <v>3.309641449789069e-11</v>
+        <v>2.621867167817982e-10</v>
       </c>
       <c r="Z21" t="n">
         <v>4.159567321693203e-07</v>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>1.073491797784859</v>
+        <v>0.6159746095322839</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>1.073491798</v>
+        <v>0.6159746112730435</v>
       </c>
       <c r="V22" t="n">
         <v>4.699641479</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>-2.151410161133072e-10</v>
+        <v>-1.740759647539392e-09</v>
       </c>
       <c r="Z22" t="n">
         <v>2.986773290913902e-06</v>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>1.073308055001895</v>
+        <v>0.6144877736389067</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>1.073308055</v>
+        <v>0.6144877736235682</v>
       </c>
       <c r="V23" t="n">
         <v>4.66702519</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
-        <v>1.895372747640067e-12</v>
+        <v>1.533850824131378e-11</v>
       </c>
       <c r="Z23" t="n">
         <v>3.363273766154862e-07</v>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>1.073121856850794</v>
+        <v>0.6129808093663686</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>1.073121857</v>
+        <v>0.6129808105740475</v>
       </c>
       <c r="V24" t="n">
         <v>4.650310797</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>-1.492059809038437e-10</v>
+        <v>-1.207678956838265e-09</v>
       </c>
       <c r="Z24" t="n">
         <v>1.488684895356585e-06</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>1.073542003629162</v>
+        <v>0.6163808280301879</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>1.073542004</v>
+        <v>0.6163808310305923</v>
       </c>
       <c r="V25" t="n">
         <v>4.741960586</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="n">
-        <v>-3.708382489975293e-10</v>
+        <v>-3.000404369402077e-09</v>
       </c>
       <c r="Z25" t="n">
         <v>3.03504387932918e-06</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1.057986785340916</v>
+        <v>0.4896048645814188</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>1.057986785</v>
+        <v>0.4896048617825537</v>
       </c>
       <c r="V26" t="n">
         <v>4.422585497</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>3.409164062162517e-10</v>
+        <v>2.798865084141511e-09</v>
       </c>
       <c r="Z26" t="n">
         <v>2.275617450031575e-06</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>1.057703527760776</v>
+        <v>0.4872790571797278</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>1.057703528</v>
+        <v>0.4872790591442451</v>
       </c>
       <c r="V27" t="n">
         <v>4.368893704</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>-2.392244180526859e-10</v>
+        <v>-1.964517271080268e-09</v>
       </c>
       <c r="Z27" t="n">
         <v>3.058229528285494e-06</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>1.058523392562856</v>
+        <v>0.4940092007923019</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>1.058523393</v>
+        <v>0.4940092043793604</v>
       </c>
       <c r="V28" t="n">
         <v>4.535916604</v>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
-        <v>-4.371440986972175e-10</v>
+        <v>-3.587058539089583e-09</v>
       </c>
       <c r="Z28" t="n">
         <v>2.255408086959676e-06</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>1.058236546680851</v>
+        <v>0.4916551202531805</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>1.058236547</v>
+        <v>0.4916551228727236</v>
       </c>
       <c r="V29" t="n">
         <v>4.518632133</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>-3.191493735954509e-10</v>
+        <v>-2.619543137960534e-09</v>
       </c>
       <c r="Z29" t="n">
         <v>6.557291269970733e-07</v>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>1.047409245191676</v>
+        <v>0.402328059592874</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>1.047409245</v>
+        <v>0.4023280580033589</v>
       </c>
       <c r="V30" t="n">
         <v>4.24165974</v>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
-        <v>1.916755643094348e-10</v>
+        <v>1.589515130628882e-09</v>
       </c>
       <c r="Z30" t="n">
         <v>1.730503582209053e-06</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>1.047465690426123</v>
+        <v>0.4027961324775978</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="U31" t="n">
-        <v>1.04746569</v>
+        <v>0.4027961289440591</v>
       </c>
       <c r="V31" t="n">
         <v>4.274205565</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>4.261233588209734e-10</v>
+        <v>3.533538683875292e-09</v>
       </c>
       <c r="Z31" t="n">
         <v>1.414413930866942e-06</v>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>1.047439362853491</v>
+        <v>0.4025778138574068</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>1.047439363</v>
+        <v>0.4025778150723308</v>
       </c>
       <c r="V32" t="n">
         <v>4.274323801</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="n">
-        <v>-1.465088050878194e-10</v>
+        <v>-1.214924050252364e-09</v>
       </c>
       <c r="Z32" t="n">
         <v>1.400952007735157e-06</v>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>1.04723672356836</v>
+        <v>0.4008972652667306</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>1.047236724</v>
+        <v>0.4008972688467997</v>
       </c>
       <c r="V33" t="n">
         <v>4.257317667</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="n">
-        <v>-4.316402790749407e-10</v>
+        <v>-3.580069074526904e-09</v>
       </c>
       <c r="Z33" t="n">
         <v>-7.89898528807953e-08</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>1.028891789399885</v>
+        <v>0.2473940309586729</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>1.028891789</v>
+        <v>0.2473940275828513</v>
       </c>
       <c r="V34" t="n">
         <v>3.712331165</v>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>3.998847919461923e-10</v>
+        <v>3.375821677753521e-09</v>
       </c>
       <c r="Z34" t="n">
         <v>-0.0001818365423211787</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>1.028852404019962</v>
+        <v>0.2470615337857998</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>1.028852404</v>
+        <v>0.2470615336172741</v>
       </c>
       <c r="V35" t="n">
         <v>3.66729707</v>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="n">
-        <v>1.996203202736524e-11</v>
+        <v>1.685256656447365e-10</v>
       </c>
       <c r="Z35" t="n">
         <v>-0.00010444528433462</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>1.028940817762783</v>
+        <v>0.247807917829614</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>1.028940818</v>
+        <v>0.2478079198321003</v>
       </c>
       <c r="V36" t="n">
         <v>3.758686253</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="n">
-        <v>-2.372169127795587e-10</v>
+        <v>-2.002486343410936e-09</v>
       </c>
       <c r="Z36" t="n">
         <v>-0.0001728188706313638</v>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>1.028842263267022</v>
+        <v>0.246975921996761</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>1.028842263</v>
+        <v>0.2469759197424533</v>
       </c>
       <c r="V37" t="n">
         <v>3.698937049</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="n">
-        <v>2.670224041878555e-10</v>
+        <v>2.254307768234654e-09</v>
       </c>
       <c r="Z37" t="n">
         <v>-8.658711445264089e-05</v>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.9999995000570615</v>
+        <v>-4.342450274561985e-06</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="U38" t="n">
-        <v>0.9999995</v>
+        <v>-4.342945904411805e-06</v>
       </c>
       <c r="V38" t="n">
         <v>10.00005614</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="n">
-        <v>5.70614666628444e-11</v>
+        <v>4.95629849820914e-10</v>
       </c>
       <c r="Z38" t="n">
         <v>1.077571809560141e-09</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.9999994782858397</v>
+        <v>-4.531552801221687e-06</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>0.999999478</v>
+        <v>-4.53403557447764e-06</v>
       </c>
       <c r="V39" t="n">
         <v>9.980742619999999</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
-        <v>2.858396852545297e-10</v>
+        <v>2.482773255952664e-09</v>
       </c>
       <c r="Z39" t="n">
         <v>2.081753489591165e-07</v>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.9999994503229138</v>
+        <v>-4.774435819342649e-06</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>0.99999945</v>
+        <v>-4.777240614573351e-06</v>
       </c>
       <c r="V40" t="n">
         <v>9.962687028</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="n">
-        <v>3.229138068050474e-10</v>
+        <v>2.804795230701204e-09</v>
       </c>
       <c r="Z40" t="n">
         <v>-2.561905247944196e-07</v>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.9999994321025444</v>
+        <v>-4.932696025857443e-06</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>0.999999432</v>
+        <v>-4.933586715855861e-06</v>
       </c>
       <c r="V41" t="n">
         <v>9.955098412</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="n">
-        <v>1.02544417401873e-10</v>
+        <v>8.906899984187665e-10</v>
       </c>
       <c r="Z41" t="n">
         <v>-3.748796970626245e-07</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>1.028793469509743</v>
+        <v>0.2465639762047215</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>1.02879347</v>
+        <v>0.2465639803438591</v>
       </c>
       <c r="V42" t="n">
         <v>3.670896512</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="n">
-        <v>-4.902569461506801e-10</v>
+        <v>-4.139137615988275e-09</v>
       </c>
       <c r="Z42" t="n">
         <v>-0.0001380126290895234</v>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1.028927411002465</v>
+        <v>0.2476947428081046</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>1.028927411</v>
+        <v>0.2476947427872946</v>
       </c>
       <c r="V43" t="n">
         <v>3.65478433</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>2.465139203877698e-12</v>
+        <v>2.08099648624227e-11</v>
       </c>
       <c r="Z43" t="n">
         <v>-9.229340032579358e-05</v>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>1.028862130907939</v>
+        <v>0.2471436507889672</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>1.028862131</v>
+        <v>0.2471436515661656</v>
       </c>
       <c r="V44" t="n">
         <v>3.749201248</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
-        <v>-9.206080342494261e-11</v>
+        <v>-7.771983889792722e-10</v>
       </c>
       <c r="Z44" t="n">
         <v>-0.0001702045004128294</v>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>1.028860469480268</v>
+        <v>0.2471296246249031</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>1.028860469</v>
+        <v>0.2471296205703675</v>
       </c>
       <c r="V45" t="n">
         <v>3.746315241</v>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="n">
-        <v>4.802676034643127e-10</v>
+        <v>4.054535596154096e-09</v>
       </c>
       <c r="Z45" t="n">
         <v>-0.0001316356105109939</v>
@@ -4204,7 +4204,7 @@
         <v>27.15708164662436</v>
       </c>
       <c r="M46" t="n">
-        <v>2.017534689387322</v>
+        <v>6.096420213904238</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -4228,7 +4228,7 @@
         <v>27.15708812</v>
       </c>
       <c r="U46" t="n">
-        <v>2.01753469</v>
+        <v>6.096420216541938</v>
       </c>
       <c r="V46" t="n">
         <v>2.548945533</v>
@@ -4240,7 +4240,7 @@
         <v>-6.47337564174677e-06</v>
       </c>
       <c r="Y46" t="n">
-        <v>-6.126779084070222e-10</v>
+        <v>-2.637700724505976e-09</v>
       </c>
       <c r="Z46" t="n">
         <v>-9.249363071006655e-07</v>
@@ -4286,7 +4286,7 @@
         <v>28.75479676629529</v>
       </c>
       <c r="M47" t="n">
-        <v>1.872335512028946</v>
+        <v>5.447673490250107</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -4310,7 +4310,7 @@
         <v>28.75480354</v>
       </c>
       <c r="U47" t="n">
-        <v>1.872335512</v>
+        <v>5.447673490115825</v>
       </c>
       <c r="V47" t="n">
         <v>2.302444723</v>
@@ -4322,7 +4322,7 @@
         <v>-6.773704715357098e-06</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.894573469802708e-11</v>
+        <v>1.342819189176225e-10</v>
       </c>
       <c r="Z47" t="n">
         <v>-5.291644500360349e-07</v>
@@ -4368,7 +4368,7 @@
         <v>30.41690396012191</v>
       </c>
       <c r="M48" t="n">
-        <v>1.748677764348117</v>
+        <v>4.854195754366977</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -4392,7 +4392,7 @@
         <v>30.416911</v>
       </c>
       <c r="U48" t="n">
-        <v>1.748677765</v>
+        <v>4.854195757604955</v>
       </c>
       <c r="V48" t="n">
         <v>2.053404767</v>
@@ -4404,7 +4404,7 @@
         <v>-7.039878084924567e-06</v>
       </c>
       <c r="Y48" t="n">
-        <v>-6.518827699864005e-10</v>
+        <v>-3.237978773995565e-09</v>
       </c>
       <c r="Z48" t="n">
         <v>-3.81617823563829e-07</v>
@@ -4450,7 +4450,7 @@
         <v>32.00252799914539</v>
       </c>
       <c r="M49" t="n">
-        <v>1.647658152360945</v>
+        <v>4.337342230433705</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -4474,7 +4474,7 @@
         <v>32.00253261</v>
       </c>
       <c r="U49" t="n">
-        <v>1.647658152</v>
+        <v>4.337342228530925</v>
       </c>
       <c r="V49" t="n">
         <v>1.832147915</v>
@@ -4486,7 +4486,7 @@
         <v>-4.610854617226323e-06</v>
       </c>
       <c r="Y49" t="n">
-        <v>3.609452736696994e-10</v>
+        <v>1.902779267481947e-09</v>
       </c>
       <c r="Z49" t="n">
         <v>1.34117063010919e-07</v>
@@ -4532,7 +4532,7 @@
         <v>10.72445661298981</v>
       </c>
       <c r="M50" t="n">
-        <v>1.799740279962512</v>
+        <v>5.104196734094612</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -4556,7 +4556,7 @@
         <v>10.72441189</v>
       </c>
       <c r="U50" t="n">
-        <v>1.79974028</v>
+        <v>5.104196734275535</v>
       </c>
       <c r="V50" t="n">
         <v>0.813257114</v>
@@ -4568,7 +4568,7 @@
         <v>4.472298981106348e-05</v>
       </c>
       <c r="Y50" t="n">
-        <v>-3.748801269409796e-11</v>
+        <v>-1.809237204497549e-10</v>
       </c>
       <c r="Z50" t="n">
         <v>5.172642111161974e-05</v>
@@ -4614,7 +4614,7 @@
         <v>10.60558382889858</v>
       </c>
       <c r="M51" t="n">
-        <v>1.814595305162068</v>
+        <v>5.175595658160765</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -4638,7 +4638,7 @@
         <v>10.6055399</v>
       </c>
       <c r="U51" t="n">
-        <v>1.814595305</v>
+        <v>5.175595657384997</v>
       </c>
       <c r="V51" t="n">
         <v>0.82997791</v>
@@ -4650,7 +4650,7 @@
         <v>4.392889857740556e-05</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.620679146441262e-10</v>
+        <v>7.757670061891986e-10</v>
       </c>
       <c r="Z51" t="n">
         <v>4.025163719845182e-05</v>
@@ -4696,7 +4696,7 @@
         <v>10.47069212890917</v>
       </c>
       <c r="M52" t="n">
-        <v>1.832158510690008</v>
+        <v>5.259260885981819</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -4720,7 +4720,7 @@
         <v>10.4706716</v>
       </c>
       <c r="U52" t="n">
-        <v>1.832158511</v>
+        <v>5.259260887451427</v>
       </c>
       <c r="V52" t="n">
         <v>0.8465123369999999</v>
@@ -4732,7 +4732,7 @@
         <v>2.052890916637296e-05</v>
       </c>
       <c r="Y52" t="n">
-        <v>-3.099918099991328e-10</v>
+        <v>-1.469608434945258e-09</v>
       </c>
       <c r="Z52" t="n">
         <v>3.440526390230403e-05</v>
@@ -4778,7 +4778,7 @@
         <v>12.13441261029543</v>
       </c>
       <c r="M53" t="n">
-        <v>1.643020455132713</v>
+        <v>4.312859406205369</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -4802,7 +4802,7 @@
         <v>12.13437115</v>
       </c>
       <c r="U53" t="n">
-        <v>1.643020455</v>
+        <v>4.312859405503779</v>
       </c>
       <c r="V53" t="n">
         <v>0.672905053</v>
@@ -4814,7 +4814,7 @@
         <v>4.146029543328211e-05</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.327127296946173e-10</v>
+        <v>7.015907854679426e-10</v>
       </c>
       <c r="Z53" t="n">
         <v>3.30657227003428e-05</v>
@@ -4860,7 +4860,7 @@
         <v>8.832428347908513</v>
       </c>
       <c r="M54" t="n">
-        <v>1.774107749358277</v>
+        <v>4.979599858174221</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -4884,7 +4884,7 @@
         <v>8.832371112000001</v>
       </c>
       <c r="U54" t="n">
-        <v>1.774107749</v>
+        <v>4.979599856420124</v>
       </c>
       <c r="V54" t="n">
         <v>0.383021632</v>
@@ -4896,7 +4896,7 @@
         <v>5.723590851225424e-05</v>
       </c>
       <c r="Y54" t="n">
-        <v>3.582774077415252e-10</v>
+        <v>1.754097311845726e-09</v>
       </c>
       <c r="Z54" t="n">
         <v>-9.67196367995804e-08</v>
@@ -4942,7 +4942,7 @@
         <v>8.701068853437642</v>
       </c>
       <c r="M55" t="n">
-        <v>1.791503459798324</v>
+        <v>5.064353024475966</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -4966,7 +4966,7 @@
         <v>8.701008131</v>
       </c>
       <c r="U55" t="n">
-        <v>1.79150346</v>
+        <v>5.064353025453766</v>
       </c>
       <c r="V55" t="n">
         <v>0.390971183</v>
@@ -4978,7 +4978,7 @@
         <v>6.072243764165819e-05</v>
       </c>
       <c r="Y55" t="n">
-        <v>-2.016755651368385e-10</v>
+        <v>-9.778000631399664e-10</v>
       </c>
       <c r="Z55" t="n">
         <v>1.088882690181148e-06</v>
@@ -5024,7 +5024,7 @@
         <v>8.675121088567986</v>
       </c>
       <c r="M56" t="n">
-        <v>1.794695952455903</v>
+        <v>5.079817667141632</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -5048,7 +5048,7 @@
         <v>8.675082428</v>
       </c>
       <c r="U56" t="n">
-        <v>1.794695953</v>
+        <v>5.079817669774931</v>
       </c>
       <c r="V56" t="n">
         <v>0.39229521</v>
@@ -5060,7 +5060,7 @@
         <v>3.866056798607076e-05</v>
       </c>
       <c r="Y56" t="n">
-        <v>-5.440974337744819e-10</v>
+        <v>-2.633298912257942e-09</v>
       </c>
       <c r="Z56" t="n">
         <v>3.210031788603018e-06</v>
@@ -5106,7 +5106,7 @@
         <v>8.642214351838183</v>
       </c>
       <c r="M57" t="n">
-        <v>1.799413598986295</v>
+        <v>5.102619966326685</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -5130,7 +5130,7 @@
         <v>8.642159592000001</v>
       </c>
       <c r="U57" t="n">
-        <v>1.799413599</v>
+        <v>5.102619966392839</v>
       </c>
       <c r="V57" t="n">
         <v>0.39481439</v>
@@ -5142,7 +5142,7 @@
         <v>5.475983818215013e-05</v>
       </c>
       <c r="Y57" t="n">
-        <v>-1.370481506057786e-11</v>
+        <v>-6.615419323452443e-11</v>
       </c>
       <c r="Z57" t="n">
         <v>-8.573336063300019e-08</v>
@@ -5188,7 +5188,7 @@
         <v>8.66945734973061</v>
       </c>
       <c r="M58" t="n">
-        <v>1.700676700723572</v>
+        <v>4.612435238310982</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -5212,7 +5212,7 @@
         <v>8.669162515</v>
       </c>
       <c r="U58" t="n">
-        <v>1.7006767</v>
+        <v>4.612435234615475</v>
       </c>
       <c r="V58" t="n">
         <v>0.230006909</v>
@@ -5224,7 +5224,7 @@
         <v>0.000294834730610205</v>
       </c>
       <c r="Y58" t="n">
-        <v>7.235716470432862e-10</v>
+        <v>3.69550701151411e-09</v>
       </c>
       <c r="Z58" t="n">
         <v>2.31684812557198e-07</v>
@@ -5270,7 +5270,7 @@
         <v>8.64870127584429</v>
       </c>
       <c r="M59" t="n">
-        <v>1.701864535305421</v>
+        <v>4.61849976466917</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -5294,7 +5294,7 @@
         <v>8.648387417</v>
       </c>
       <c r="U59" t="n">
-        <v>1.701864535</v>
+        <v>4.618499763110375</v>
       </c>
       <c r="V59" t="n">
         <v>0.226751147</v>
@@ -5306,7 +5306,7 @@
         <v>0.000313858844290138</v>
       </c>
       <c r="Y59" t="n">
-        <v>3.054214658959609e-10</v>
+        <v>1.558794870959446e-09</v>
       </c>
       <c r="Z59" t="n">
         <v>2.22923422388277e-07</v>
@@ -5352,7 +5352,7 @@
         <v>8.616784556735269</v>
       </c>
       <c r="M60" t="n">
-        <v>1.705767135136349</v>
+        <v>4.638394852830881</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -5376,7 +5376,7 @@
         <v>8.616481828</v>
       </c>
       <c r="U60" t="n">
-        <v>1.705767135</v>
+        <v>4.63839485213658</v>
       </c>
       <c r="V60" t="n">
         <v>0.226306024</v>
@@ -5388,7 +5388,7 @@
         <v>0.0003027287352690422</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.363493762340795e-10</v>
+        <v>6.943015051774637e-10</v>
       </c>
       <c r="Z60" t="n">
         <v>2.860111827929224e-08</v>
@@ -5434,7 +5434,7 @@
         <v>8.625723295281627</v>
       </c>
       <c r="M61" t="n">
-        <v>1.704066903867348</v>
+        <v>4.629732834552734</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -5458,7 +5458,7 @@
         <v>8.62540446</v>
       </c>
       <c r="U61" t="n">
-        <v>1.704066904</v>
+        <v>4.629732835228883</v>
       </c>
       <c r="V61" t="n">
         <v>0.2249004</v>
@@ -5470,7 +5470,7 @@
         <v>0.0003188352816270168</v>
       </c>
       <c r="Y61" t="n">
-        <v>-1.326523335620777e-10</v>
+        <v>-6.761489146356325e-10</v>
       </c>
       <c r="Z61" t="n">
         <v>2.495207962194268e-07</v>

--- a/PlayGround/Verification Freq_Metrics/FreqMetrics_Reference_Python.xlsx
+++ b/PlayGround/Verification Freq_Metrics/FreqMetrics_Reference_Python.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
